--- a/test_project.xlsx
+++ b/test_project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\warehouse_mgr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1646F200-0EFD-473F-A22F-1D0419B60406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417228EF-83C0-4E8A-9BA5-DD794AF903B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{08FF9CDE-0D8B-47C9-8436-443386A1BE7B}"/>
   </bookViews>
